--- a/medical_surveys_questionnaires/041_covid_19_daily_status_update_form--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/041_covid_19_daily_status_update_form--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nausea</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nausea</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>vomiting</t>
+          <t>abdominal_pain</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vomiting</t>
+          <t>Abdominal Pain</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>abdominal_pain</t>
+          <t>abdominal_cramping</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Abdominal Pain</t>
+          <t>Abdominal Cramping</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>abdominal_cramping</t>
+          <t>dizziness</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Abdominal Cramping</t>
+          <t>Dizziness</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>dizziness</t>
+          <t>muscle_aches</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dizziness</t>
+          <t>Muscle Aches</t>
         </is>
       </c>
     </row>
@@ -1052,27 +1052,10 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>muscle_aches</t>
+          <t>joint_pain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>Muscle Aches</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>joint_pain</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
         <is>
           <t>Joint Pain</t>
         </is>
